--- a/histograms/histogram_CalcT_K_.xlsx
+++ b/histograms/histogram_CalcT_K_.xlsx
@@ -445,7 +445,7 @@
         <v>508</v>
       </c>
       <c r="B2" t="n">
-        <v>386</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>648</v>
       </c>
       <c r="B4" t="n">
-        <v>1357</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>858</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         <v>998</v>
       </c>
       <c r="B9" t="n">
-        <v>731</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>1068</v>
       </c>
       <c r="B10" t="n">
-        <v>2837</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>1138</v>
       </c>
       <c r="B11" t="n">
-        <v>268</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>1208</v>
       </c>
       <c r="B12" t="n">
-        <v>935</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>1278</v>
       </c>
       <c r="B13" t="n">
-        <v>3918</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>1348</v>
       </c>
       <c r="B14" t="n">
-        <v>10117</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>1418</v>
       </c>
       <c r="B15" t="n">
-        <v>2005</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>1488</v>
       </c>
       <c r="B16" t="n">
-        <v>2421</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>1558</v>
       </c>
       <c r="B17" t="n">
-        <v>779</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -581,7 +581,7 @@
         <v>1698</v>
       </c>
       <c r="B19" t="n">
-        <v>220</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -597,7 +597,7 @@
         <v>1838</v>
       </c>
       <c r="B21" t="n">
-        <v>338</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
